--- a/output/female_ECGs_features_calculated (Age).xlsx
+++ b/output/female_ECGs_features_calculated (Age).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ECGBiologicalAge\ECGHiguchi\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3606FD1-E79E-4BCB-944D-C3A79386BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F021B26D-498D-41EA-B442-9E83919BD142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{256D619C-1760-4473-9900-0695644AA1AF}"/>
   </bookViews>
@@ -11691,7 +11691,7 @@
         <v>22</v>
       </c>
       <c r="C238" s="1">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(LEFT(B238,FIND(" -",B238)-1), MID(B238,FIND("-",B238)+2,LEN(B238)))</f>
         <v>37</v>
       </c>
       <c r="D238" s="2">

--- a/output/female_ECGs_features_calculated (Age).xlsx
+++ b/output/female_ECGs_features_calculated (Age).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ECGBiologicalAge\ECGHiguchi\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F021B26D-498D-41EA-B442-9E83919BD142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E4A280-4AFD-4BE1-87B2-292AB536A12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{256D619C-1760-4473-9900-0695644AA1AF}"/>
   </bookViews>
@@ -1071,7 +1071,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="1">
-        <f t="shared" ref="C2:C65" si="0">AVERAGE(LEFT(B2,FIND(" -",B2)-1), MID(B2,FIND("-",B2)+2,LEN(B2)))</f>
+        <f>AVERAGE(LEFT(B2,FIND(" -",B2)-1), MID(B2,FIND("-",B2)+2,LEN(B2)))</f>
         <v>22</v>
       </c>
       <c r="D2" s="2">
@@ -1116,7 +1116,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C2:C65" si="0">AVERAGE(LEFT(B3,FIND(" -",B3)-1), MID(B3,FIND("-",B3)+2,LEN(B3)))</f>
         <v>22</v>
       </c>
       <c r="D3" s="2">
